--- a/astro-site/public/dl/kit-tareas-pasteleria/07-plantilla-personalizable.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/07-plantilla-personalizable.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Por Franja Horaria" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Por Zona" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Por Perfil" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Franja Horaria" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Zona" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Perfil" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Por Franja Horaria'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Por Zona'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Por Perfil'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,6 +96,12 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -137,7 +147,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -159,68 +169,118 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="34">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="7" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -582,13 +642,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B10"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -596,6 +657,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -603,9 +665,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -641,8 +701,24 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «Hecha» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -651,18 +727,18 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -679,10 +755,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -722,18 +799,16 @@
           <t xml:space="preserve">  Madrugada / Inicio Producción (04:00 - 07:00)</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="31" t="n"/>
+      <c r="E5" s="31" t="n"/>
+      <c r="F5" s="31" t="n"/>
+      <c r="G5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="33" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr"/>
       <c r="C6" s="11" t="inlineStr">
@@ -747,10 +822,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="33" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr"/>
       <c r="C7" s="11" t="inlineStr">
@@ -764,10 +837,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="33" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr"/>
       <c r="C8" s="11" t="inlineStr">
@@ -781,10 +852,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="33" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr"/>
       <c r="C9" s="11" t="inlineStr">
@@ -798,10 +867,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="33" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr"/>
       <c r="C10" s="11" t="inlineStr">
@@ -814,24 +881,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Mañana / Producción Principal (07:00 - 12:00)</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="32" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="33" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr"/>
       <c r="C13" s="11" t="inlineStr">
@@ -845,10 +911,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="33" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr"/>
       <c r="C14" s="11" t="inlineStr">
@@ -862,10 +926,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="33" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr"/>
       <c r="C15" s="11" t="inlineStr">
@@ -879,10 +941,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="33" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr"/>
       <c r="C16" s="11" t="inlineStr">
@@ -896,10 +956,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="33" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr"/>
       <c r="C17" s="11" t="inlineStr">
@@ -912,24 +970,23 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="15" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Tarde / Producción + Venta (12:00 - 17:00)</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
+      <c r="B19" s="31" t="n"/>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+      <c r="E19" s="31" t="n"/>
+      <c r="F19" s="31" t="n"/>
+      <c r="G19" s="32" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="33" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr"/>
       <c r="C20" s="11" t="inlineStr">
@@ -943,10 +1000,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="33" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr"/>
       <c r="C21" s="11" t="inlineStr">
@@ -960,10 +1015,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="33" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr"/>
       <c r="C22" s="11" t="inlineStr">
@@ -977,10 +1030,8 @@
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="33" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr"/>
       <c r="C23" s="11" t="inlineStr">
@@ -994,10 +1045,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="33" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr"/>
       <c r="C24" s="11" t="inlineStr">
@@ -1010,24 +1059,23 @@
       <c r="F24" s="14" t="n"/>
       <c r="G24" s="15" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cierre (17:00 - 20:00)</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
+      <c r="B26" s="31" t="n"/>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+      <c r="E26" s="31" t="n"/>
+      <c r="F26" s="31" t="n"/>
+      <c r="G26" s="32" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="33" t="n">
+        <v>16</v>
       </c>
       <c r="B27" s="10" t="inlineStr"/>
       <c r="C27" s="11" t="inlineStr">
@@ -1041,10 +1089,8 @@
       <c r="G27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="33" t="n">
+        <v>17</v>
       </c>
       <c r="B28" s="10" t="inlineStr"/>
       <c r="C28" s="11" t="inlineStr">
@@ -1058,10 +1104,8 @@
       <c r="G28" s="15" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A29" s="33" t="n">
+        <v>18</v>
       </c>
       <c r="B29" s="10" t="inlineStr"/>
       <c r="C29" s="11" t="inlineStr">
@@ -1075,10 +1119,8 @@
       <c r="G29" s="15" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A30" s="33" t="n">
+        <v>19</v>
       </c>
       <c r="B30" s="10" t="inlineStr"/>
       <c r="C30" s="11" t="inlineStr">
@@ -1091,6 +1133,8 @@
       <c r="F30" s="14" t="n"/>
       <c r="G30" s="15" t="n"/>
     </row>
+    <row r="31"/>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
@@ -1099,7 +1143,7 @@
       </c>
       <c r="D33" s="16">
         <f>COUNTIF(F5:F31,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E33" s="17" t="inlineStr">
         <is>
@@ -1110,6 +1154,7 @@
         <v>19</v>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
@@ -1117,13 +1162,17 @@
         </is>
       </c>
       <c r="B35" s="15" t="n"/>
+      <c r="C35" s="31" t="n"/>
+      <c r="D35" s="32" t="n"/>
       <c r="E35" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F35" s="15" t="n"/>
-    </row>
+      <c r="G35" s="32" t="n"/>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="18" t="inlineStr">
         <is>
@@ -1144,11 +1193,20 @@
     <mergeCell ref="A33:C33"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F27 F28 F29 F30" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F27 F28 F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1157,18 +1215,18 @@
   <sheetPr>
     <tabColor rgb="00FF8C00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1185,10 +1243,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1228,18 +1287,16 @@
           <t xml:space="preserve">  Obrador</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n"/>
-      <c r="C5" s="20" t="n"/>
-      <c r="D5" s="20" t="n"/>
-      <c r="E5" s="20" t="n"/>
-      <c r="F5" s="20" t="n"/>
-      <c r="G5" s="20" t="n"/>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="31" t="n"/>
+      <c r="E5" s="31" t="n"/>
+      <c r="F5" s="31" t="n"/>
+      <c r="G5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="33" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr"/>
       <c r="C6" s="21" t="inlineStr">
@@ -1253,10 +1310,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="33" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr"/>
       <c r="C7" s="21" t="inlineStr">
@@ -1270,10 +1325,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="33" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr"/>
       <c r="C8" s="21" t="inlineStr">
@@ -1287,10 +1340,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="33" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr"/>
       <c r="C9" s="21" t="inlineStr">
@@ -1304,10 +1355,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="33" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr"/>
       <c r="C10" s="21" t="inlineStr">
@@ -1320,24 +1369,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Horno</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n"/>
-      <c r="C12" s="23" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="23" t="n"/>
-      <c r="F12" s="23" t="n"/>
-      <c r="G12" s="23" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="32" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="33" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr"/>
       <c r="C13" s="24" t="inlineStr">
@@ -1351,10 +1399,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="33" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr"/>
       <c r="C14" s="24" t="inlineStr">
@@ -1368,10 +1414,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="33" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr"/>
       <c r="C15" s="24" t="inlineStr">
@@ -1385,10 +1429,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="33" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr"/>
       <c r="C16" s="24" t="inlineStr">
@@ -1401,24 +1443,23 @@
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="15" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  Vitrina / Despacho</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n"/>
-      <c r="C18" s="26" t="n"/>
-      <c r="D18" s="26" t="n"/>
-      <c r="E18" s="26" t="n"/>
-      <c r="F18" s="26" t="n"/>
-      <c r="G18" s="26" t="n"/>
+      <c r="B18" s="31" t="n"/>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+      <c r="E18" s="31" t="n"/>
+      <c r="F18" s="31" t="n"/>
+      <c r="G18" s="32" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="33" t="n">
+        <v>10</v>
       </c>
       <c r="B19" s="10" t="inlineStr"/>
       <c r="C19" s="27" t="inlineStr">
@@ -1432,10 +1473,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="33" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr"/>
       <c r="C20" s="27" t="inlineStr">
@@ -1449,10 +1488,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="33" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr"/>
       <c r="C21" s="27" t="inlineStr">
@@ -1466,10 +1503,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="33" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr"/>
       <c r="C22" s="27" t="inlineStr">
@@ -1482,24 +1517,23 @@
       <c r="F22" s="14" t="n"/>
       <c r="G22" s="15" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  Almacén / Cámaras</t>
         </is>
       </c>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="15" t="n"/>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="B24" s="31" t="n"/>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+      <c r="E24" s="31" t="n"/>
+      <c r="F24" s="31" t="n"/>
+      <c r="G24" s="32" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="33" t="n">
+        <v>14</v>
       </c>
       <c r="B25" s="10" t="inlineStr"/>
       <c r="C25" s="29" t="inlineStr">
@@ -1513,10 +1547,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="33" t="n">
+        <v>15</v>
       </c>
       <c r="B26" s="10" t="inlineStr"/>
       <c r="C26" s="29" t="inlineStr">
@@ -1530,10 +1562,8 @@
       <c r="G26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="33" t="n">
+        <v>16</v>
       </c>
       <c r="B27" s="10" t="inlineStr"/>
       <c r="C27" s="29" t="inlineStr">
@@ -1547,10 +1577,8 @@
       <c r="G27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="33" t="n">
+        <v>17</v>
       </c>
       <c r="B28" s="10" t="inlineStr"/>
       <c r="C28" s="29" t="inlineStr">
@@ -1563,6 +1591,8 @@
       <c r="F28" s="14" t="n"/>
       <c r="G28" s="15" t="n"/>
     </row>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
@@ -1571,7 +1601,7 @@
       </c>
       <c r="D31" s="16">
         <f>COUNTIF(F5:F29,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E31" s="17" t="inlineStr">
         <is>
@@ -1582,6 +1612,7 @@
         <v>17</v>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
@@ -1589,13 +1620,17 @@
         </is>
       </c>
       <c r="B33" s="15" t="n"/>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="32" t="n"/>
       <c r="E33" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F33" s="15" t="n"/>
-    </row>
+      <c r="G33" s="32" t="n"/>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="18" t="inlineStr">
         <is>
@@ -1616,11 +1651,20 @@
     <mergeCell ref="A31:C31"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F19 F20 F21 F22 F25 F26 F27 F28" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F19 F20 F21 F22 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1629,18 +1673,18 @@
   <sheetPr>
     <tabColor rgb="009C27B0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1657,10 +1701,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1700,18 +1745,16 @@
           <t xml:space="preserve">  Jefe Pastelero / Chef Pâtissier</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="31" t="n"/>
+      <c r="E5" s="31" t="n"/>
+      <c r="F5" s="31" t="n"/>
+      <c r="G5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="33" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr"/>
       <c r="C6" s="11" t="inlineStr">
@@ -1725,10 +1768,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="33" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr"/>
       <c r="C7" s="11" t="inlineStr">
@@ -1742,10 +1783,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="33" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr"/>
       <c r="C8" s="11" t="inlineStr">
@@ -1759,10 +1798,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="33" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr"/>
       <c r="C9" s="11" t="inlineStr">
@@ -1775,24 +1812,23 @@
       <c r="F9" s="14" t="n"/>
       <c r="G9" s="15" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pastelero / Oficial</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="31" t="n"/>
+      <c r="D11" s="31" t="n"/>
+      <c r="E11" s="31" t="n"/>
+      <c r="F11" s="31" t="n"/>
+      <c r="G11" s="32" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="33" t="n">
+        <v>5</v>
       </c>
       <c r="B12" s="10" t="inlineStr"/>
       <c r="C12" s="11" t="inlineStr">
@@ -1806,10 +1842,8 @@
       <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="33" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr"/>
       <c r="C13" s="11" t="inlineStr">
@@ -1823,10 +1857,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="33" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr"/>
       <c r="C14" s="11" t="inlineStr">
@@ -1840,10 +1872,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="33" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr"/>
       <c r="C15" s="11" t="inlineStr">
@@ -1856,24 +1886,23 @@
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="15" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Ayudante de Pastelería</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
+      <c r="B17" s="31" t="n"/>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+      <c r="E17" s="31" t="n"/>
+      <c r="F17" s="31" t="n"/>
+      <c r="G17" s="32" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="33" t="n">
+        <v>9</v>
       </c>
       <c r="B18" s="10" t="inlineStr"/>
       <c r="C18" s="11" t="inlineStr">
@@ -1887,10 +1916,8 @@
       <c r="G18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="33" t="n">
+        <v>10</v>
       </c>
       <c r="B19" s="10" t="inlineStr"/>
       <c r="C19" s="11" t="inlineStr">
@@ -1904,10 +1931,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="33" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr"/>
       <c r="C20" s="11" t="inlineStr">
@@ -1921,10 +1946,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="33" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr"/>
       <c r="C21" s="11" t="inlineStr">
@@ -1937,24 +1960,23 @@
       <c r="F21" s="14" t="n"/>
       <c r="G21" s="15" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Dependiente / Vitrina</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
+      <c r="B23" s="31" t="n"/>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+      <c r="E23" s="31" t="n"/>
+      <c r="F23" s="31" t="n"/>
+      <c r="G23" s="32" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="33" t="n">
+        <v>13</v>
       </c>
       <c r="B24" s="10" t="inlineStr"/>
       <c r="C24" s="11" t="inlineStr">
@@ -1968,10 +1990,8 @@
       <c r="G24" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="33" t="n">
+        <v>14</v>
       </c>
       <c r="B25" s="10" t="inlineStr"/>
       <c r="C25" s="11" t="inlineStr">
@@ -1985,10 +2005,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="33" t="n">
+        <v>15</v>
       </c>
       <c r="B26" s="10" t="inlineStr"/>
       <c r="C26" s="11" t="inlineStr">
@@ -2002,10 +2020,8 @@
       <c r="G26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="33" t="n">
+        <v>16</v>
       </c>
       <c r="B27" s="10" t="inlineStr"/>
       <c r="C27" s="11" t="inlineStr">
@@ -2018,6 +2034,8 @@
       <c r="F27" s="14" t="n"/>
       <c r="G27" s="15" t="n"/>
     </row>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
@@ -2026,7 +2044,7 @@
       </c>
       <c r="D30" s="16">
         <f>COUNTIF(F5:F28,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
@@ -2037,6 +2055,7 @@
         <v>16</v>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
@@ -2044,13 +2063,17 @@
         </is>
       </c>
       <c r="B32" s="15" t="n"/>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="32" t="n"/>
       <c r="E32" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F32" s="15" t="n"/>
-    </row>
+      <c r="G32" s="32" t="n"/>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
@@ -2071,10 +2094,19 @@
     <mergeCell ref="A11:G11"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F12 F13 F14 F15 F18 F19 F20 F21 F24 F25 F26 F27" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F18 F19 F20 F21 F24 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-pasteleria/07-plantilla-personalizable.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/07-plantilla-personalizable.xlsx
@@ -280,6 +280,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -705,14 +715,15 @@
     <row r="12">
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>Marca con ✓ en la columna «Hecha» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -729,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -784,7 +795,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1133,48 +1144,84 @@
       <c r="F30" s="14" t="n"/>
       <c r="G30" s="15" t="n"/>
     </row>
-    <row r="31"/>
-    <row r="32"/>
+    <row r="31">
+      <c r="A31" s="33" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="15" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="33" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="15" t="n"/>
+    </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="33" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="15" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="33" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="15" t="n"/>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D33" s="16">
-        <f>COUNTIF(F5:F31,"✓")</f>
+      <c r="D36" s="16">
+        <f>COUNTIF(F5:F34,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E33" s="17" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F33" s="16" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="F36" s="16">
+        <f>COUNTIF(B5:B34,"?*")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n"/>
-      <c r="C35" s="31" t="n"/>
-      <c r="D35" s="32" t="n"/>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="31" t="n"/>
+      <c r="D38" s="32" t="n"/>
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F35" s="15" t="n"/>
-      <c r="G35" s="32" t="n"/>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="32" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -1182,19 +1229,24 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="F35:G35"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B38:D38"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="F38:G38"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G34">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F27 F28 F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F27 F28 F29 F30 F31 F32 F33 F34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1217,7 +1269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1272,7 +1324,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1591,48 +1643,84 @@
       <c r="F28" s="14" t="n"/>
       <c r="G28" s="15" t="n"/>
     </row>
-    <row r="29"/>
-    <row r="30"/>
+    <row r="29">
+      <c r="A29" s="33" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="29" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="15" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="15" t="n"/>
+    </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="33" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="15" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="33" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="15" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D31" s="16">
-        <f>COUNTIF(F5:F29,"✓")</f>
+      <c r="D34" s="16">
+        <f>COUNTIF(F5:F32,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F31" s="16" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="F34" s="16">
+        <f>COUNTIF(B5:B32,"?*")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B33" s="15" t="n"/>
-      <c r="C33" s="31" t="n"/>
-      <c r="D33" s="32" t="n"/>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="31" t="n"/>
+      <c r="D36" s="32" t="n"/>
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F33" s="15" t="n"/>
-      <c r="G33" s="32" t="n"/>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="32" t="n"/>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -1642,17 +1730,22 @@
   <mergeCells count="9">
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="F33:G33"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A18:G18"/>
-    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="A24:G24"/>
+    <mergeCell ref="F36:G36"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="B36:D36"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G32">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F19 F20 F21 F22 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F19 F20 F21 F22 F25 F26 F27 F28 F29 F30 F31 F32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1675,7 +1768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1730,7 +1823,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2034,48 +2127,84 @@
       <c r="F27" s="14" t="n"/>
       <c r="G27" s="15" t="n"/>
     </row>
-    <row r="28"/>
-    <row r="29"/>
+    <row r="28">
+      <c r="A28" s="33" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="15" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="33" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="15" t="n"/>
+    </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="33" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="15" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="15" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D30" s="16">
-        <f>COUNTIF(F5:F28,"✓")</f>
+      <c r="D33" s="16">
+        <f>COUNTIF(F5:F31,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F30" s="16" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="F33" s="16">
+        <f>COUNTIF(B5:B31,"?*")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B32" s="15" t="n"/>
-      <c r="C32" s="31" t="n"/>
-      <c r="D32" s="32" t="n"/>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="31" t="n"/>
+      <c r="D35" s="32" t="n"/>
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="32" t="n"/>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="32" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -2083,19 +2212,24 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A23:G23"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A33:C33"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G31">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F18 F19 F20 F21 F24 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F18 F19 F20 F21 F24 F25 F26 F27 F28 F29 F30 F31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
